--- a/reports/meta-llama_Meta-Llama-3-70B-Instruct.xlsx
+++ b/reports/meta-llama_Meta-Llama-3-70B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-10 23:18:49</t>
+          <t>2026-02-24 21:19:24</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/12 (75.0%)</t>
+          <t>8/12 (66.7%)</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17/25 (68.0%)</t>
+          <t>18/25 (72.0%)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17/34 (50.0%)</t>
+          <t>16/34 (47.1%)</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/15 (40.0%)</t>
+          <t>7/15 (46.7%)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>72/81 (88.9%)</t>
+          <t>71/81 (87.7%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>48/67 (71.6%)</t>
+          <t>49/67 (73.1%)</t>
         </is>
       </c>
     </row>
@@ -1026,9 +1026,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2148,9 +2148,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6395,9 +6395,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7112,9 +7112,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8452,9 +8452,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -10490,9 +10490,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B241" s="12" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B241" s="11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -18209,9 +18209,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1039" s="12" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1039" s="11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -19516,9 +19516,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1172" s="11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B1172" s="12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>

--- a/reports/meta-llama_Meta-Llama-3-70B-Instruct.xlsx
+++ b/reports/meta-llama_Meta-Llama-3-70B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-24 21:19:24</t>
+          <t>2026-03-07 03:01:02</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9/12 (75.0%)</t>
+          <t>7/12 (58.3%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17/37 (45.9%)</t>
+          <t>15/37 (40.5%)</t>
         </is>
       </c>
     </row>
@@ -1622,9 +1622,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -1700,9 +1700,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9526,9 +9526,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -9676,9 +9676,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>

--- a/reports/meta-llama_Meta-Llama-3-70B-Instruct.xlsx
+++ b/reports/meta-llama_Meta-Llama-3-70B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08 13:14:41</t>
+          <t>2026-03-10 18:51:35</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3/10 (30.0%)</t>
+          <t>4/10 (40.0%)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13/34 (38.2%)</t>
+          <t>15/34 (44.1%)</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8/15 (53.3%)</t>
+          <t>9/15 (60.0%)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>74/83 (89.2%)</t>
+          <t>75/83 (90.4%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>47/74 (63.5%)</t>
+          <t>48/74 (64.9%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14/37 (37.8%)</t>
+          <t>16/37 (43.2%)</t>
         </is>
       </c>
     </row>
@@ -2928,9 +2928,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6845,9 +6845,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7217,9 +7217,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7873,9 +7873,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -12285,9 +12285,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B388" s="12" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B388" s="11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -19424,9 +19424,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1123" s="12" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1123" s="11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -20099,9 +20099,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1193" s="12" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1193" s="11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -21303,9 +21303,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1312" s="12" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1312" s="11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
